--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83238</v>
+        <v>16.90366</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60461</v>
+        <v>16.40009</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74772</v>
+        <v>16.8063</v>
       </c>
       <c r="F2" t="n">
-        <v>42.49994</v>
+        <v>42.09512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04933</v>
+        <v>0.05058</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86306</v>
+        <v>1.7909</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.49077</v>
+        <v>16.85148</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48747</v>
+        <v>16.46562</v>
       </c>
       <c r="E3" t="n">
-        <v>16.76891</v>
+        <v>16.83474</v>
       </c>
       <c r="F3" t="n">
-        <v>42.30386</v>
+        <v>41.49725</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05091</v>
+        <v>0.05052</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82568</v>
+        <v>1.78597</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.73917</v>
+        <v>17.16</v>
       </c>
       <c r="D4" t="n">
-        <v>16.40379</v>
+        <v>16.64969</v>
       </c>
       <c r="E4" t="n">
-        <v>16.69139</v>
+        <v>16.93849</v>
       </c>
       <c r="F4" t="n">
-        <v>41.88153</v>
+        <v>42.2511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05142</v>
+        <v>0.05152</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79822</v>
+        <v>1.83607</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.70932</v>
+        <v>16.65259</v>
       </c>
       <c r="D6" t="n">
-        <v>16.05674</v>
+        <v>15.82974</v>
       </c>
       <c r="E6" t="n">
-        <v>16.29985</v>
+        <v>16.63556</v>
       </c>
       <c r="F6" t="n">
-        <v>21.63694</v>
+        <v>21.1823</v>
       </c>
       <c r="G6" t="n">
-        <v>34.55515</v>
+        <v>34.61863</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87845</v>
+        <v>16.94216</v>
       </c>
       <c r="D7" t="n">
-        <v>15.67353</v>
+        <v>16.42451</v>
       </c>
       <c r="E7" t="n">
-        <v>16.33443</v>
+        <v>16.71099</v>
       </c>
       <c r="F7" t="n">
-        <v>21.73176</v>
+        <v>21.89054</v>
       </c>
       <c r="G7" t="n">
-        <v>34.57762</v>
+        <v>33.57838</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65388</v>
+        <v>16.7855</v>
       </c>
       <c r="D8" t="n">
-        <v>16.19018</v>
+        <v>15.9819</v>
       </c>
       <c r="E8" t="n">
-        <v>16.81933</v>
+        <v>16.6206</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81442</v>
+        <v>21.78849</v>
       </c>
       <c r="G8" t="n">
-        <v>33.98264</v>
+        <v>34.38513</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5940299999999999</v>
+        <v>0.61144</v>
       </c>
       <c r="D10" t="n">
-        <v>1.09545</v>
+        <v>1.11602</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61696</v>
+        <v>0.6067900000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11261</v>
+        <v>1.12365</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59902</v>
+        <v>0.60937</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10398</v>
+        <v>1.1203</v>
       </c>
     </row>
   </sheetData>
